--- a/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
+++ b/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z78"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -545,6 +545,16 @@
       <c r="Z1" t="inlineStr">
         <is>
           <t>ubigeo</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>dre</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ugel</t>
         </is>
       </c>
     </row>
@@ -621,6 +631,8 @@
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -691,6 +703,8 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -765,6 +779,8 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -839,6 +855,8 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -913,6 +931,8 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -987,6 +1007,8 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1061,6 +1083,8 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1131,6 +1155,8 @@
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1203,6 +1229,8 @@
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1277,6 +1305,8 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1347,6 +1377,8 @@
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1455,6 +1487,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1605,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1671,6 +1723,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1777,6 +1839,16 @@
       <c r="Z16" t="inlineStr">
         <is>
           <t>150605</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
     </row>
@@ -1863,6 +1935,8 @@
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1971,6 +2045,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2079,6 +2163,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2187,6 +2281,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2295,6 +2399,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2403,6 +2517,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2511,6 +2635,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2619,6 +2753,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2727,6 +2871,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2835,6 +2989,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2943,6 +3107,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3051,6 +3225,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3159,6 +3343,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3267,6 +3461,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3375,6 +3579,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3483,6 +3697,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3591,6 +3815,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3699,6 +3933,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3807,6 +4051,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3915,6 +4169,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4023,6 +4287,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4131,6 +4405,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4239,6 +4523,16 @@
           <t>150605</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4347,6 +4641,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4455,6 +4759,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4563,6 +4877,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4671,6 +4995,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4779,6 +5113,16 @@
           <t>150604</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4887,6 +5231,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4995,6 +5349,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5103,6 +5467,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5211,6 +5585,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5319,6 +5703,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5427,6 +5821,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5535,6 +5939,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5643,6 +6057,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5751,6 +6175,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5859,6 +6293,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5967,6 +6411,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6075,6 +6529,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6183,6 +6647,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6291,6 +6765,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6399,6 +6883,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -6507,6 +7001,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -6615,6 +7119,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -6723,6 +7237,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -6831,6 +7355,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -6939,6 +7473,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7047,6 +7591,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7155,6 +7709,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7263,6 +7827,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7371,6 +7945,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -7479,6 +8063,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -7587,6 +8181,16 @@
           <t>150604</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -7695,6 +8299,16 @@
           <t>150604</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -7803,6 +8417,16 @@
           <t>150604</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -7911,6 +8535,16 @@
           <t>150604</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8019,6 +8653,16 @@
           <t>150604</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8127,6 +8771,16 @@
           <t>150604</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8235,6 +8889,16 @@
           <t>150601</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -8341,6 +9005,16 @@
       <c r="Z77" t="inlineStr">
         <is>
           <t>150604</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
     </row>
@@ -8417,6 +9091,8 @@
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
+++ b/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB78"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -555,6 +555,11 @@
       <c r="AB1" t="inlineStr">
         <is>
           <t>ugel</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>fuente</t>
         </is>
       </c>
     </row>
@@ -633,6 +638,11 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr"/>
@@ -705,6 +715,11 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
@@ -781,6 +796,11 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
@@ -857,6 +877,11 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
@@ -933,6 +958,11 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr"/>
@@ -1009,6 +1039,11 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr"/>
@@ -1085,6 +1120,11 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr"/>
@@ -1157,6 +1197,11 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr"/>
@@ -1231,6 +1276,11 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
@@ -1307,6 +1357,11 @@
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
@@ -1379,6 +1434,11 @@
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1497,6 +1557,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1615,6 +1680,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1733,6 +1803,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1851,6 +1926,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1929,14 +2009,47 @@
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
-      <c r="X17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>559012</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="Y17" t="inlineStr"/>
-      <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>150601</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2055,6 +2168,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2173,6 +2291,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2291,6 +2414,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2409,6 +2537,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2527,6 +2660,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2645,6 +2783,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2763,6 +2906,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2881,6 +3029,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2999,6 +3152,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3117,6 +3275,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3235,6 +3398,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3353,6 +3521,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3471,6 +3644,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3589,6 +3767,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3707,6 +3890,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3825,6 +4013,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3943,6 +4136,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4061,6 +4259,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4179,6 +4382,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4297,6 +4505,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4415,6 +4628,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4533,6 +4751,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4651,6 +4874,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4769,6 +4997,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4887,6 +5120,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5005,6 +5243,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5123,6 +5366,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5241,6 +5489,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5359,6 +5612,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5477,6 +5735,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5595,6 +5858,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -5713,6 +5981,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -5831,6 +6104,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5949,6 +6227,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6067,6 +6350,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6185,6 +6473,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6303,6 +6596,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6421,6 +6719,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6539,6 +6842,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6657,6 +6965,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -6775,6 +7088,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -6893,6 +7211,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7011,6 +7334,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7129,6 +7457,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7247,6 +7580,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7365,6 +7703,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7483,6 +7826,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7601,6 +7949,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7719,6 +8072,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -7837,6 +8195,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -7955,6 +8318,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8073,6 +8441,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8191,6 +8564,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8309,6 +8687,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8427,6 +8810,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8545,6 +8933,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8663,6 +9056,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8781,6 +9179,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -8899,6 +9302,11 @@
           <t>UGEL 10 HUARAL</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9015,6 +9423,11 @@
       <c r="AB77" t="inlineStr">
         <is>
           <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
         </is>
       </c>
     </row>
@@ -9093,6 +9506,11 @@
       <c r="Z78" t="inlineStr"/>
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>DIGEGED</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
+++ b/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC78"/>
+  <dimension ref="A1:AE78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -558,6 +558,16 @@
         </is>
       </c>
       <c r="AC1" t="inlineStr">
+        <is>
+          <t>nombre_ie</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -631,14 +641,28 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -708,14 +732,28 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>DRE APURÍMAC</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -796,7 +834,9 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -877,7 +917,9 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr">
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -958,7 +1000,9 @@
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr">
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1039,7 +1083,9 @@
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
       <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr">
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1120,7 +1166,9 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr">
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1190,14 +1238,28 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTÍN</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1276,7 +1338,9 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
       <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr">
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1350,14 +1414,28 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1427,14 +1505,28 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1559,6 +1651,16 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
+          <t>AUGUSTO SALAZAR BONDY</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1682,6 +1784,16 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
+          <t>34/34/CET 34</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1805,6 +1917,16 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
+          <t>21557 INMACULADA CONCEPCION/21557 INMACULADA CONCEPCION/21557 INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -1928,6 +2050,16 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
+          <t>CESAR VALLEJO</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2047,6 +2179,16 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
+          <t>SOR ANA DE LOS ANGELES</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2170,6 +2312,16 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
+          <t>PEQUEÑA BELEN/PEQUEÑA BELEN/PEQUEÑA BELEN</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2293,6 +2445,16 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
+          <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ/21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2416,6 +2578,16 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
+          <t>20390 HORTENCIA DULANTO DE LAS CASAS/20390 HORTENCIA DULANTO DE LAS CASAS</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2539,6 +2711,16 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
+          <t>20391 JORGE BRAVO DE RUEDA QUEROL/20391 JORGE BRAVO DE RUEDA QUEROL</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2662,6 +2844,16 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
+          <t>345 MARIA ISABEL LANDEO GALA</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2785,6 +2977,16 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
+          <t>20392 JUAN PASCUAL PRINGLES/20392 JUAN PASCUAL PRINGLES/20392 JUAN PASCUAL PRINGLES</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -2908,6 +3110,16 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
+          <t>377 SANTISIMA TRINIDAD</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3031,6 +3243,16 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
+          <t>20394 JORGE ORTIZ DUEÑAS/20394 JORGE ORTIZ DUEÑAS</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3154,6 +3376,16 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
+          <t>21570 ESTRELLITA DE BELEN/21570 ESTRELLITA DE BELEN</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3277,6 +3509,16 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
+          <t>ESTRELLA DE LA MAÑANA</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3400,6 +3642,16 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
+          <t>20393 TUPAC AMARU/20393 TUPAC AMARU/20393 TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3523,6 +3775,16 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
+          <t>VIRGEN DE LA CANDELARIA/VIRGEN DE LA CANDELARIA/VIRGEN DE LA CANDELARIA</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3646,6 +3908,16 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
+          <t>20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3769,6 +4041,16 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
+          <t>20881 SANTISIMA VIRGEN MARIA/20881 SANTISIMA VIRGEN MARIA</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -3892,6 +4174,16 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
+          <t>21556 LOS VENCEDORES DE TORRE BLANCA/21556 LOS VENCEDORES DE TORRE BLANCA</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4015,6 +4307,16 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
+          <t>EL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4138,6 +4440,16 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
+          <t>20395 NUESTRA SEÑORA DE FATIMA/20395 NUESTRA SEÑORA DE FATIMA/20395 NUESTRA SEÑORA DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4261,6 +4573,16 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
+          <t>490 JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4384,6 +4706,16 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
+          <t>SEÑOR DE LA SOLEDAD/SEÑOR DE LA SOLEDAD/SEÑOR DE LA SOLEDAD</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4507,6 +4839,16 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
+          <t>20788 JUAN VELAZCO ALVARADO/20788 JUAN VELASCO ALVARADO</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4630,6 +4972,16 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
+          <t>518 SEÑOR DE LOS MILAGROS</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4753,6 +5105,16 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
+          <t>85 MARIA INMACULADA CONCEPCION</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4876,6 +5238,16 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
+          <t>326 SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -4999,6 +5371,16 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
+          <t>546 SAN ANTONIO</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5122,6 +5504,16 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
+          <t>20402 VIRGEN DE FATIMA</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5245,6 +5637,16 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
+          <t>20826 SAN JUAN BAUTISTA/20826 SAN JUAN BAUTISTA</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5368,6 +5770,16 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
+          <t>21554 JOSE OLAYA/21554 JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5491,6 +5903,16 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
+          <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5614,6 +6036,16 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
+          <t>21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5737,6 +6169,16 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
+          <t>20406</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5860,6 +6302,16 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
+          <t>20902 TUPAC AMARU/20902 TUPAC AMARU/20902 TUPAC AMARU</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -5983,6 +6435,16 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
+          <t>20399 LA ESPERANZA/20399 LA ESPERANZA/20399 LA ESPERANZA</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6106,6 +6568,16 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
+          <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN/20793 LIBERTADOR DON JOSE DE SAN MARTIN/20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6229,6 +6701,16 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
+          <t>21562 OSCAR BERCKEMEYER PAZOS/21562 OSCAR BERCKEMEYER PAZOS/21562 OSCAR BERCKEMEYER PAZOS</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6352,6 +6834,16 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
+          <t>EL ANGEL/EL ANGEL</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6475,6 +6967,16 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
+          <t>CONTIGO PERU/CONTIGO PERU</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6598,6 +7100,16 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
+          <t>20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6721,6 +7233,16 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
+          <t>20865 LA FLORIDA/20865 LA FLORIDA</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6844,6 +7366,16 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
+          <t>20845 MARIANO MELGAR/20845 MARIANO MELGAR</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -6967,6 +7499,16 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
+          <t>402 SANTA MARIA</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7090,6 +7632,16 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7213,6 +7765,16 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
+          <t>20453 SANTA TERESITA DEL NIÑO JESUS</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7336,6 +7898,16 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
+          <t>20407/20407</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7459,6 +8031,16 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
+          <t>NIÑOS TALENTOSOS</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7582,6 +8164,16 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
+          <t>400 VIRGEN DEL ROSARIO</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7705,6 +8297,16 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
+          <t>20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7828,6 +8430,16 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
+          <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -7951,6 +8563,16 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
+          <t>87 EMILIA BARCIA BONIFFATTI</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8074,6 +8696,16 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
+          <t>20401/20401</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8197,6 +8829,16 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
+          <t>100/100/100</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8320,6 +8962,16 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
+          <t>547 ANTONIO GRAÑA REYES</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8443,6 +9095,16 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
+          <t>20403 CARLOS MARTINEZ URIBE/20403 CARLOS MARTINEZ URIBE</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8566,6 +9228,16 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
+          <t>21554 JOSE OLAYA/21554 JOSE OLAYA</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8689,6 +9361,16 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
+          <t>20386 JORGE BASADRE/20386 JORGE BASADRE/20386 JORGE BASADRE</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8812,6 +9494,16 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
+          <t>21571 SAN JUAN DE DIOS/21571 SAN JUAN DE DIOS</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -8935,6 +9627,16 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
+          <t>21551 CAPITAN JUAN VICENTE SUAREZ/21551 CAPITAN JUAN VICENTE SUAREZ/21551 CAPITAN JUAN VICENTE SUAREZ</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9058,6 +9760,16 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
+          <t>333 LASTENIA FEBRES DE VIZQUERRA</t>
+        </is>
+      </c>
+      <c r="AD74" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE74" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9181,6 +9893,16 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
+          <t>20444 JOSE ALEJANDRO LOPEZ DURAND/20444 JOSE ALEJANDRO LOPEZ DURAND/20444 JOSE ALEJANDRO LOPEZ DURAND</t>
+        </is>
+      </c>
+      <c r="AD75" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE75" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9304,6 +10026,16 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
+          <t>21010 CLARA NICHOS MANSILLA/21010 CLARA NICHOS MANSILLA</t>
+        </is>
+      </c>
+      <c r="AD76" t="inlineStr">
+        <is>
+          <t>Urbana</t>
+        </is>
+      </c>
+      <c r="AE76" t="inlineStr">
+        <is>
           <t>DIGEGED</t>
         </is>
       </c>
@@ -9426,6 +10158,16 @@
         </is>
       </c>
       <c r="AC77" t="inlineStr">
+        <is>
+          <t>21550 NUESTRA SEÑORA DE LA MERCED/21550 NUESTRA SEÑORA DE LA MERCED/21550 NUESTRA SEÑORA DE LA MERCED</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>Rural</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9499,14 +10241,28 @@
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
-      <c r="AB78" t="inlineStr"/>
-      <c r="AC78" t="inlineStr">
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>

--- a/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
+++ b/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
@@ -419,102 +419,102 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Codigo Modular</t>
+          <t>cod_mod</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>AÑO</t>
+          <t>ano</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DRE/GRE</t>
+          <t>dre_gre</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Unidad Ejecutora</t>
+          <t>unidad_ejecutora</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>UGEL</t>
+          <t>ugel</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Producto</t>
+          <t>producto</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Actividad</t>
+          <t>actividad</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Unidad de medida</t>
+          <t>unidad_de_medida</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Meta Fisica Programada (Cantidad)</t>
+          <t>meta_fisica_programada_cantidad</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Detalle de la Unidad de Medida (Nombre del Servicio contratado)</t>
+          <t>detalle_de_la_unidad_de_medida_nombre_del_servicio_contratad</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Centro Poblado</t>
+          <t>centro_poblado</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Nivel</t>
+          <t>nivel</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>SIAGIE 2025</t>
+          <t>siagie_2025</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Intervención Culminada (Si/No)</t>
+          <t>intervencion_culminada_si_no</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>PIM 2025</t>
+          <t>pim_2025</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Fuentes de Financiamiento</t>
+          <t>fuentes_de_financiamiento</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>¿Como se ejecutaran los recursos asignados?</t>
+          <t>como_se_ejecutaran_los_recursos_asignados</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>OBS</t>
+          <t>obs</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>ETAPA</t>
+          <t>etapa</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>FECHA DE INFORMACION</t>
+          <t>fecha_de_informacion</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>centro_poblado</t>
+          <t>centro_poblado_2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
@@ -554,7 +554,7 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>ugel</t>
+          <t>ugel_2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">

--- a/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
+++ b/output/bases_limpias/Grupo_09_OTROS/df_digeged_otros25.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE78"/>
+  <dimension ref="A1:AB78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,70 +504,55 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>obs</t>
+          <t>cod_local</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>etapa</t>
+          <t>departamento</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>fecha_de_informacion</t>
+          <t>provincia</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>cod_local</t>
+          <t>distrito</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>departamento</t>
+          <t>centro_poblado_2</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>provincia</t>
+          <t>ubigeo</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>distrito</t>
+          <t>dre</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>centro_poblado_2</t>
+          <t>ugel_2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>ubigeo</t>
+          <t>nombre_ie</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>dre</t>
+          <t>area</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
-        <is>
-          <t>ugel_2</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>nombre_ie</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>area</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
         <is>
           <t>fuente</t>
         </is>
@@ -638,31 +623,28 @@
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ANCASH</t>
+        </is>
+      </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>ANCASH</t>
-        </is>
-      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>DRE ANCASH</t>
+        </is>
+      </c>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
       <c r="AB2" t="inlineStr">
-        <is>
-          <t>DRE ANCASH</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -729,31 +711,28 @@
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>APURIMAC</t>
+        </is>
+      </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>APURIMAC</t>
-        </is>
-      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>DRE APURIMAC</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>DRE APURÍMAC</t>
+        </is>
+      </c>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>DRE APURIMAC</t>
-        </is>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
-        <is>
-          <t>DRE APURÍMAC</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -833,10 +812,7 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -916,10 +892,7 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -999,10 +972,7 @@
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
       <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1082,10 +1052,7 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1165,10 +1132,7 @@
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1235,31 +1199,28 @@
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
+      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTÍN</t>
+        </is>
+      </c>
       <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
+      <c r="AA9" t="inlineStr"/>
       <c r="AB9" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTÍN</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1337,10 +1298,7 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1411,31 +1369,28 @@
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
+      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>UGEL LAMAS</t>
+        </is>
+      </c>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
+      <c r="AA11" t="inlineStr"/>
       <c r="AB11" t="inlineStr">
-        <is>
-          <t>UGEL LAMAS</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1502,31 +1457,28 @@
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>SAN MARTIN</t>
+        </is>
+      </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>SAN MARTIN</t>
-        </is>
-      </c>
+      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>DRE SAN MARTIN</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>UGEL RIOJA</t>
+        </is>
+      </c>
       <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>DRE SAN MARTIN</t>
-        </is>
-      </c>
+      <c r="AA12" t="inlineStr"/>
       <c r="AB12" t="inlineStr">
-        <is>
-          <t>UGEL RIOJA</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1606,60 +1558,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>355977</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>355977</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>AUGUSTO SALAZAR BONDY</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>AUGUSTO SALAZAR BONDY</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE13" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1739,60 +1688,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>355963</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>355963</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>34/34/CET 34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>34/34/CET 34</t>
-        </is>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -1872,60 +1818,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>354666</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>354666</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CUYO</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>CUYO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>21557 INMACULADA CONCEPCION/21557 INMACULADA CONCEPCION/21557 INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>21557 INMACULADA CONCEPCION/21557 INMACULADA CONCEPCION/21557 INMACULADA CONCEPCION</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2005,60 +1948,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>355982</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>355982</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>CESAR VALLEJO</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2138,56 +2078,53 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>559012</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>559012</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
+          <t>HUARAL</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>HUARAL</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>UGEL 10 HUARAL</t>
+        </is>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>SOR ANA DE LOS ANGELES</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>SOR ANA DE LOS ANGELES</t>
-        </is>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2267,60 +2204,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>734110</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>734110</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PELAVILLO</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>PELAVILLO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>PEQUEÑA BELEN/PEQUEÑA BELEN/PEQUEÑA BELEN</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>PEQUEÑA BELEN/PEQUEÑA BELEN/PEQUEÑA BELEN</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2400,60 +2334,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>356024</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>356024</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ/21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>21008 LUIS ALBERTO DE LAS CASAS ARRIZ/21008 LUIS ALBERTO DE LAS CASAS ARRIZ</t>
-        </is>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2533,60 +2464,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>355920</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>355920</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20390 HORTENCIA DULANTO DE LAS CASAS/20390 HORTENCIA DULANTO DE LAS CASAS</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>20390 HORTENCIA DULANTO DE LAS CASAS/20390 HORTENCIA DULANTO DE LAS CASAS</t>
-        </is>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2666,60 +2594,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>356019</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>356019</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20391 JORGE BRAVO DE RUEDA QUEROL/20391 JORGE BRAVO DE RUEDA QUEROL</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>20391 JORGE BRAVO DE RUEDA QUEROL/20391 JORGE BRAVO DE RUEDA QUEROL</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2799,60 +2724,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>355835</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>355835</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PELAVILLO</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>PELAVILLO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>345 MARIA ISABEL LANDEO GALA</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>345 MARIA ISABEL LANDEO GALA</t>
-        </is>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -2932,60 +2854,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>355958</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>355958</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PERALVILLO</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>PERALVILLO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20392 JUAN PASCUAL PRINGLES/20392 JUAN PASCUAL PRINGLES/20392 JUAN PASCUAL PRINGLES</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>20392 JUAN PASCUAL PRINGLES/20392 JUAN PASCUAL PRINGLES/20392 JUAN PASCUAL PRINGLES</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3065,60 +2984,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>355840</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>355840</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CERRO TRINIDAD</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>CERRO TRINIDAD</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>377 SANTISIMA TRINIDAD</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>377 SANTISIMA TRINIDAD</t>
-        </is>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3198,60 +3114,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>355816</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>355816</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PUERTO CHANCAY</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>PUERTO CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20394 JORGE ORTIZ DUEÑAS/20394 JORGE ORTIZ DUEÑAS</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>20394 JORGE ORTIZ DUEÑAS/20394 JORGE ORTIZ DUEÑAS</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3331,60 +3244,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>734252</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>734252</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>21570 ESTRELLITA DE BELEN/21570 ESTRELLITA DE BELEN</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>21570 ESTRELLITA DE BELEN/21570 ESTRELLITA DE BELEN</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3464,60 +3374,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>734351</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>734351</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>ESTRELLA DEL MAÑANA</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>ESTRELLA DEL MAÑANA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>ESTRELLA DE LA MAÑANA</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>ESTRELLA DE LA MAÑANA</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3597,60 +3504,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>356000</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>356000</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PAMPA LIBRE</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>PAMPA LIBRE</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20393 TUPAC AMARU/20393 TUPAC AMARU/20393 TUPAC AMARU</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>20393 TUPAC AMARU/20393 TUPAC AMARU/20393 TUPAC AMARU</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3730,60 +3634,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>355878</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>355878</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>LA CANDELARIA</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>LA CANDELARIA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>VIRGEN DE LA CANDELARIA/VIRGEN DE LA CANDELARIA/VIRGEN DE LA CANDELARIA</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>VIRGEN DE LA CANDELARIA/VIRGEN DE LA CANDELARIA/VIRGEN DE LA CANDELARIA</t>
-        </is>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3863,60 +3764,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>355944</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>355944</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAYLLO</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>CHANCAYLLO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION/20799 DANIEL ALCIDES CARRION</t>
-        </is>
-      </c>
-      <c r="AD30" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE30" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -3996,60 +3894,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>355897</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>355897</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>BUENA VISTA</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>BUENA VISTA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20881 SANTISIMA VIRGEN MARIA/20881 SANTISIMA VIRGEN MARIA</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>20881 SANTISIMA VIRGEN MARIA/20881 SANTISIMA VIRGEN MARIA</t>
-        </is>
-      </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4129,60 +4024,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>355901</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>355901</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>TORRE BLANCA</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>TORRE BLANCA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>21556 LOS VENCEDORES DE TORRE BLANCA/21556 LOS VENCEDORES DE TORRE BLANCA</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>21556 LOS VENCEDORES DE TORRE BLANCA/21556 LOS VENCEDORES DE TORRE BLANCA</t>
-        </is>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4262,60 +4154,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>080209</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>080209</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>ALDEA CAMPESINA</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>ALDEA CAMPESINA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>EL ROSARIO</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>EL ROSARIO</t>
-        </is>
-      </c>
-      <c r="AD33" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE33" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4395,60 +4284,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>355864</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>355864</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>QUEPEPAMPA</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>QUEPEPAMPA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20395 NUESTRA SEÑORA DE FATIMA/20395 NUESTRA SEÑORA DE FATIMA/20395 NUESTRA SEÑORA DE FATIMA</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>20395 NUESTRA SEÑORA DE FATIMA/20395 NUESTRA SEÑORA DE FATIMA/20395 NUESTRA SEÑORA DE FATIMA</t>
-        </is>
-      </c>
-      <c r="AD34" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE34" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4528,60 +4414,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>355821</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>355821</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PAMPA LIBRE</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>PAMPA LIBRE</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>490 JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>490 JOSE DE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD35" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE35" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4661,60 +4544,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>566098</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>566098</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>LA SOLEDAD</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>LA SOLEDAD</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>SEÑOR DE LA SOLEDAD/SEÑOR DE LA SOLEDAD/SEÑOR DE LA SOLEDAD</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>SEÑOR DE LA SOLEDAD/SEÑOR DE LA SOLEDAD/SEÑOR DE LA SOLEDAD</t>
-        </is>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4794,60 +4674,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>355915</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>355915</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>VILLA PROGRESO</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>VILLA PROGRESO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>20788 JUAN VELAZCO ALVARADO/20788 JUAN VELASCO ALVARADO</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>20788 JUAN VELAZCO ALVARADO/20788 JUAN VELASCO ALVARADO</t>
-        </is>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -4927,60 +4804,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>355779</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>355779</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>ASOVICEM</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>ASOVICEM</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>518 SEÑOR DE LOS MILAGROS</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>518 SEÑOR DE LOS MILAGROS</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5060,60 +4934,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>355802</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>355802</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHANCAY</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>CHANCAY</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>150605</t>
+          <t>85 MARIA INMACULADA CONCEPCION</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>85 MARIA INMACULADA CONCEPCION</t>
-        </is>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5193,60 +5064,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>354732</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>354732</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>LOS NATURALES</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>LOS NATURALES</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>326 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>326 SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5326,60 +5194,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>354713</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>354713</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>546 SAN ANTONIO</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>546 SAN ANTONIO</t>
-        </is>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5459,60 +5324,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>354911</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>354911</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20402 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>20402 VIRGEN DE FATIMA</t>
-        </is>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5592,60 +5454,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>355005</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>355005</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>SAN JUAN 4</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>SAN JUAN 4</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20826 SAN JUAN BAUTISTA/20826 SAN JUAN BAUTISTA</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>20826 SAN JUAN BAUTISTA/20826 SAN JUAN BAUTISTA</t>
-        </is>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5725,60 +5584,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>355618</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>355618</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PALPA</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>PALPA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>21554 JOSE OLAYA/21554 JOSE OLAYA</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>21554 JOSE OLAYA/21554 JOSE OLAYA</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE44" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5858,60 +5714,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>354727</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>354727</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>BUENOS AIRES</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>BUENOS AIRES</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>03 VIRGEN DE LA MEDALLA MILAGROSA</t>
-        </is>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -5991,60 +5844,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>354869</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>354869</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUANDO</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>HUANDO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE/21559 ANTONIO GRAÑA ELIZALDE</t>
-        </is>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -6124,60 +5974,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>354968</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
-          <t>354968</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>LA HUAQUILLA</t>
         </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>LA HUAQUILLA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>20406</t>
-        </is>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -6257,60 +6104,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>734153</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>734153</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>TUPAC AMARU</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>TUPAC AMARU</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20902 TUPAC AMARU/20902 TUPAC AMARU/20902 TUPAC AMARU</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>20902 TUPAC AMARU/20902 TUPAC AMARU/20902 TUPAC AMARU</t>
-        </is>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE48" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -6390,60 +6234,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>354671</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>354671</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>ESPERANZA BAJA</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>ESPERANZA BAJA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20399 LA ESPERANZA/20399 LA ESPERANZA/20399 LA ESPERANZA</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>20399 LA ESPERANZA/20399 LA ESPERANZA/20399 LA ESPERANZA</t>
-        </is>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE49" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -6523,60 +6364,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>355067</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>355067</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>SAN MARTIN DE RETES</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>SAN MARTIN DE RETES</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN/20793 LIBERTADOR DON JOSE DE SAN MARTIN/20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>20793 LIBERTADOR DON JOSE DE SAN MARTIN/20793 LIBERTADOR DON JOSE DE SAN MARTIN/20793 LIBERTADOR DON JOSE DE SAN MARTIN</t>
-        </is>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE50" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -6656,60 +6494,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>354609</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>354609</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>JESUS DEL VALLE</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>JESUS DEL VALLE</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>21562 OSCAR BERCKEMEYER PAZOS/21562 OSCAR BERCKEMEYER PAZOS/21562 OSCAR BERCKEMEYER PAZOS</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>21562 OSCAR BERCKEMEYER PAZOS/21562 OSCAR BERCKEMEYER PAZOS/21562 OSCAR BERCKEMEYER PAZOS</t>
-        </is>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -6789,60 +6624,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>504270</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>504270</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>EL ANGEL</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>EL ANGEL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>EL ANGEL/EL ANGEL</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>EL ANGEL/EL ANGEL</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -6922,60 +6754,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>354614</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>354614</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CONTIGO PERU</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>CONTIGO PERU</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>CONTIGO PERU/CONTIGO PERU</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>CONTIGO PERU/CONTIGO PERU</t>
-        </is>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7055,60 +6884,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>354586</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>354586</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CABUYAL</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>CABUYAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON/20396 ANTONIO ARELLANO BUITRON</t>
-        </is>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7188,60 +7014,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>355048</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>355048</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CABAYAL ALTO</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>CABAYAL ALTO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20865 LA FLORIDA/20865 LA FLORIDA</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>20865 LA FLORIDA/20865 LA FLORIDA</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7321,60 +7144,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>354987</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>354987</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>EL TREBOL</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>EL TREBOL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20845 MARIANO MELGAR/20845 MARIANO MELGAR</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>20845 MARIANO MELGAR/20845 MARIANO MELGAR</t>
-        </is>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE56" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7454,60 +7274,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>354572</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>354572</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>EL TREBOL</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>EL TREBOL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>402 SANTA MARIA</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>402 SANTA MARIA</t>
-        </is>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE57" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7587,60 +7404,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>354893</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>354893</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>NUEVA ESTRELLA</t>
         </is>
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>NUEVA ESTRELLA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>SAGRADO CORAZON DE JESUS/SAGRADO CORAZON DE JESUS</t>
-        </is>
-      </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE58" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7720,60 +7534,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>354949</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>354949</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CERRO SAN CRISTOBAL</t>
         </is>
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>CERRO SAN CRISTOBAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20453 SANTA TERESITA DEL NIÑO JESUS</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>20453 SANTA TERESITA DEL NIÑO JESUS</t>
-        </is>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE59" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7853,60 +7664,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>354992</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>354992</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V60" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>GARCIA ALONSO</t>
         </is>
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>GARCIA ALONSO</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20407/20407</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>20407/20407</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -7986,60 +7794,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr"/>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>770037</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U61" t="inlineStr">
         <is>
-          <t>770037</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V61" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W61" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>NIÑOS TALENTOSOS</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>NIÑOS TALENTOSOS</t>
-        </is>
-      </c>
-      <c r="AD61" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE61" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -8119,60 +7924,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr"/>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>354690</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U62" t="inlineStr">
         <is>
-          <t>354690</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V62" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W62" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>400 VIRGEN DEL ROSARIO</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>400 VIRGEN DEL ROSARIO</t>
-        </is>
-      </c>
-      <c r="AD62" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE62" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -8252,60 +8054,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr"/>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>354973</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>354973</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V63" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES/20449 ANDRES DE LOS REYES</t>
-        </is>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE63" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -8385,60 +8184,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr"/>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>354591</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U64" t="inlineStr">
         <is>
-          <t>354591</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V64" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>LA HUAQUILLA</t>
         </is>
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>LA HUAQUILLA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>373 NUESTRA SEÑORA DE LA VICTORIA</t>
-        </is>
-      </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE64" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -8518,60 +8314,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr"/>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>354746</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U65" t="inlineStr">
         <is>
-          <t>354746</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V65" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>87 EMILIA BARCIA BONIFFATTI</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>87 EMILIA BARCIA BONIFFATTI</t>
-        </is>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE65" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -8651,60 +8444,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr"/>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>354751</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U66" t="inlineStr">
         <is>
-          <t>354751</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V66" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>ESQUIVEL</t>
         </is>
       </c>
       <c r="W66" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>ESQUIVEL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20401/20401</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>20401/20401</t>
-        </is>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE66" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -8784,60 +8574,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>355053</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U67" t="inlineStr">
         <is>
-          <t>355053</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V67" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>JESUS DEL VALLE</t>
         </is>
       </c>
       <c r="W67" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>JESUS DEL VALLE</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>100/100/100</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>100/100/100</t>
-        </is>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE67" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -8917,60 +8704,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr"/>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>354633</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U68" t="inlineStr">
         <is>
-          <t>354633</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V68" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W68" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>547 ANTONIO GRAÑA REYES</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>547 ANTONIO GRAÑA REYES</t>
-        </is>
-      </c>
-      <c r="AD68" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE68" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9050,60 +8834,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr"/>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>354794</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U69" t="inlineStr">
         <is>
-          <t>354794</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V69" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W69" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>20403 CARLOS MARTINEZ URIBE/20403 CARLOS MARTINEZ URIBE</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>20403 CARLOS MARTINEZ URIBE/20403 CARLOS MARTINEZ URIBE</t>
-        </is>
-      </c>
-      <c r="AD69" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE69" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9183,60 +8964,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr"/>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>355618</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U70" t="inlineStr">
         <is>
-          <t>355618</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V70" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PALPA</t>
         </is>
       </c>
       <c r="W70" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>PALPA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>21554 JOSE OLAYA/21554 JOSE OLAYA</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>21554 JOSE OLAYA/21554 JOSE OLAYA</t>
-        </is>
-      </c>
-      <c r="AD70" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE70" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9316,60 +9094,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr"/>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>355722</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U71" t="inlineStr">
         <is>
-          <t>355722</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="W71" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>20386 JORGE BASADRE/20386 JORGE BASADRE/20386 JORGE BASADRE</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>20386 JORGE BASADRE/20386 JORGE BASADRE/20386 JORGE BASADRE</t>
-        </is>
-      </c>
-      <c r="AD71" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE71" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9449,60 +9224,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr"/>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>355736</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>355736</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="W72" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>SAN JUAN DE DIOS</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>21571 SAN JUAN DE DIOS/21571 SAN JUAN DE DIOS</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>21571 SAN JUAN DE DIOS/21571 SAN JUAN DE DIOS</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9582,60 +9354,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr"/>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>355675</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>355675</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CAQUI</t>
         </is>
       </c>
       <c r="W73" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>CAQUI</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>21551 CAPITAN JUAN VICENTE SUAREZ/21551 CAPITAN JUAN VICENTE SUAREZ/21551 CAPITAN JUAN VICENTE SUAREZ</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>21551 CAPITAN JUAN VICENTE SUAREZ/21551 CAPITAN JUAN VICENTE SUAREZ/21551 CAPITAN JUAN VICENTE SUAREZ</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9715,60 +9484,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr"/>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>355699</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>355699</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>PALPA</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>PALPA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>333 LASTENIA FEBRES DE VIZQUERRA</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>333 LASTENIA FEBRES DE VIZQUERRA</t>
-        </is>
-      </c>
-      <c r="AD74" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE74" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9848,60 +9614,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>355595</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>355595</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>CHACRA Y MAR</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>CHACRA Y MAR</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>20444 JOSE ALEJANDRO LOPEZ DURAND/20444 JOSE ALEJANDRO LOPEZ DURAND/20444 JOSE ALEJANDRO LOPEZ DURAND</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>20444 JOSE ALEJANDRO LOPEZ DURAND/20444 JOSE ALEJANDRO LOPEZ DURAND/20444 JOSE ALEJANDRO LOPEZ DURAND</t>
-        </is>
-      </c>
-      <c r="AD75" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE75" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -9981,60 +9744,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr"/>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>354770</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>354770</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>HUARAL</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>150601</t>
+          <t>21010 CLARA NICHOS MANSILLA/21010 CLARA NICHOS MANSILLA</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Urbana</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>21010 CLARA NICHOS MANSILLA/21010 CLARA NICHOS MANSILLA</t>
-        </is>
-      </c>
-      <c r="AD76" t="inlineStr">
-        <is>
-          <t>Urbana</t>
-        </is>
-      </c>
-      <c r="AE76" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -10114,60 +9874,57 @@
           <t>Visita a II.EE. para seguimiento de refuerzo escolar, continuidad educativa y acceso a la matrícula digital.</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr"/>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>355604</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>HUARAL</t>
+        </is>
+      </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>355604</t>
+          <t>AUCALLAMA</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
         <is>
-          <t>LIMA PROVINCIAS</t>
+          <t>BOZA</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>HUARAL</t>
+          <t>150604</t>
         </is>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>AUCALLAMA</t>
+          <t>DRE LIMA PROVINCIAS</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>BOZA</t>
+          <t>UGEL 10 HUARAL</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>150604</t>
+          <t>21550 NUESTRA SEÑORA DE LA MERCED/21550 NUESTRA SEÑORA DE LA MERCED/21550 NUESTRA SEÑORA DE LA MERCED</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>DRE LIMA PROVINCIAS</t>
+          <t>Rural</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
-        <is>
-          <t>UGEL 10 HUARAL</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>21550 NUESTRA SEÑORA DE LA MERCED/21550 NUESTRA SEÑORA DE LA MERCED/21550 NUESTRA SEÑORA DE LA MERCED</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>Rural</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
@@ -10238,31 +9995,28 @@
         </is>
       </c>
       <c r="R78" t="inlineStr"/>
-      <c r="S78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>LIMA PROVINCIAS</t>
+        </is>
+      </c>
       <c r="T78" t="inlineStr"/>
       <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr">
-        <is>
-          <t>LIMA PROVINCIAS</t>
-        </is>
-      </c>
+      <c r="V78" t="inlineStr"/>
       <c r="W78" t="inlineStr"/>
-      <c r="X78" t="inlineStr"/>
-      <c r="Y78" t="inlineStr"/>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>DRE LIMA PROVINCIAS</t>
+        </is>
+      </c>
       <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr">
-        <is>
-          <t>DRE LIMA PROVINCIAS</t>
-        </is>
-      </c>
+      <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr">
-        <is>
-          <t>DRE LIMA PROVINCIAS</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr"/>
-      <c r="AD78" t="inlineStr"/>
-      <c r="AE78" t="inlineStr">
         <is>
           <t>DIGEGED</t>
         </is>
